--- a/CDF_Heating_Element_Power_Tolerance/SplineCDF_Fall2025_Heat Elem Tol.xlsx
+++ b/CDF_Heating_Element_Power_Tolerance/SplineCDF_Fall2025_Heat Elem Tol.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Heating_Element_Power_Tolerance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07146DBB-E3C5-4BD1-96FB-1F706FF6A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{07146DBB-E3C5-4BD1-96FB-1F706FF6A85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357478CC-8E6D-4C01-9D32-7B030B297454}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6509,103 +6509,103 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.18</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-8.3783783783782928E-3</v>
+        <v>-1.6666666666666774E-3</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>3.6756756756756562E-2</v>
+        <v>1.1666666666666679E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.12162162162162175</v>
+        <v>0.04</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>1.2333333333333323</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.95671072191522788</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.95671072191522788</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-20.931668400971439</v>
+        <v>-40.333333333333002</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-9.5792378259904503</v>
+        <v>-81.407407407406353</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-316.72218531637589</v>
+        <v>-773.3333333333162</v>
       </c>
       <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>18.429938541625617</v>
+        <v>49.296296296295687</v>
       </c>
       <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>2.6414433176435592</v>
+        <v>3.6666666666666514</v>
       </c>
       <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>1.3078957837705547</v>
+        <v>0.59936328097424707</v>
       </c>
       <c r="S2">
         <f ca="1">-Q2</f>
-        <v>-2.6414433176435592</v>
+        <v>-3.6666666666666514</v>
       </c>
       <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>0.90646284875017058</v>
+        <v>0.98010872128129278</v>
       </c>
       <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.73142006501543022</v>
+        <v>0.34374508491765693</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>1.4623655913978568</v>
+        <v>2.333333333333321</v>
       </c>
       <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>6.251106060444422</v>
+        <v>9.5207972893961053</v>
       </c>
       <c r="X2">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-2.8640092862508508</v>
+        <v>-2.5207972893961412</v>
       </c>
       <c r="Y2">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>1.0000000000000002</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="e">
         <f ca="1">-N2/2+SQRT(O2)</f>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>1.0000000000000002</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36463,15 +36463,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36609,6 +36600,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36616,14 +36616,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F2C8B1-26F5-4087-9C20-592A1F2739FF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04AED7DC-B3BF-4D28-BB7E-289D232902FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36641,6 +36633,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23F2C8B1-26F5-4087-9C20-592A1F2739FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19310A6F-400B-49A2-880E-4E39559D9DD4}">
   <ds:schemaRefs>
